--- a/plantillas/modelo/modelo_acs_v1.xlsx
+++ b/plantillas/modelo/modelo_acs_v1.xlsx
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>MONASTERIO DE POBLET 30</t>
+          <t/>
         </is>
       </c>
       <c r="D4" s="22" t="n"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>ES0208330332121001LR</t>
+          <t/>
         </is>
       </c>
       <c r="D5" s="22" t="n"/>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>MONASTERIO DE POBLET 30</t>
+          <t/>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>ES0031300016174003ZK0F</t>
+          <t/>
         </is>
       </c>
       <c r="F5" s="7" t="n"/>
@@ -9089,7 +9089,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ZARAGOZA + ECOCIUDAD VALDESPARTERA</t>
+          <t>SUMINISTRO DE AGUA</t>
         </is>
       </c>
     </row>
@@ -14586,13 +14586,10 @@
           <t>LECTURAS CONTADORES ACS</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 121*2+125,24*6</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="n">
-        <v>993.4400000000001</v>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45">
+        <f>B6*12</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14625,18 +14622,12 @@
           <t>MANTENIMIENTO SALA CALDERAS</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
-        <v>123.35</v>
-      </c>
+      <c r="B9" s="45" t="n"/>
       <c r="C9" s="45">
         <f>B9*12</f>
-        <v/>
-      </c>
-      <c r="E9" s="180" t="inlineStr">
-        <is>
-          <t>50% acs 50% calefacción</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="180"/>
     </row>
     <row r="10">
       <c r="A10" s="44" t="inlineStr">
@@ -14650,7 +14641,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EJERCICIO 2023-2024 (Agosto a Julio)</t>
+          <t>EJERCICIO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -14945,7 +14936,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>LECTURAS ACS (GOMEZ)</t>
+          <t>LECTURAS ACS</t>
         </is>
       </c>
     </row>
